--- a/data/excel/cheques_2025.xlsx
+++ b/data/excel/cheques_2025.xlsx
@@ -7,8 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Août" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Septembre" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Janvier" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Février" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mars" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Avril" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mai" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Juin" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Juillet" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Août" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Septembre" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Octobre" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Novembre" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Décembre" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,32 +81,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -464,33 +462,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Date d'émission</t>
+          <t>Date réc</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Type de Règlement</t>
+          <t>Type rég</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Numéro du chèque</t>
+          <t>N° doc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Banque/Agence</t>
+          <t>Bq/Agce</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Banque de dépôts - Agence</t>
+          <t>Bq dép. - Agce</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -500,12 +514,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Nom du déposant</t>
+          <t>Nom dép</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Montant</t>
+          <t>Mont</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -515,12 +529,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Date d'échéance</t>
+          <t>Date éch</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Date de Création</t>
+          <t>Date créat</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -535,7 +549,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Date de facture</t>
+          <t>Date fact</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -544,335 +558,326 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>32323</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Ewew</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>fdfdfdf</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>11213</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>45884</v>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>ANNULE</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>32323</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Ewew</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>fdfdfdf</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>11213</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>15/08/2025</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>ANNULE</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>13232</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>Ewew</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>fdfdfdf</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>1300</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>45877</v>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>23323</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Ewew</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>1323</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>45877</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>09/08/2025</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>15546</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - Agence 01</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - Agence 01</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Isly</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PLS</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>09/08/2025</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>09/08/2025</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>ENCAISSE</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -885,33 +890,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Date d'émission</t>
+          <t>Date réc</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Type de Règlement</t>
+          <t>Type rég</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Numéro du chèque</t>
+          <t>N° doc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Banque/Agence</t>
+          <t>Bq/Agce</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Banque de dépôts - Agence</t>
+          <t>Bq dép. - Agce</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -921,12 +942,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Nom du déposant</t>
+          <t>Nom dép</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Montant</t>
+          <t>Mont</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -936,12 +957,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Date d'échéance</t>
+          <t>Date éch</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Date de Création</t>
+          <t>Date créat</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -956,7 +977,649 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Date de facture</t>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -968,7 +1631,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -976,45 +1639,47 @@
           <t>CHQ</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Al Barid Bank - sfdf</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Ewew</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>fdfdfdf</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Al Barid Bank - dsdsd</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Al Barid Bank - dsdsd</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Fikri El Fakir</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>dsdsd</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2154</v>
+        <v>1323</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>MAD</t>
         </is>
       </c>
-      <c r="J2" s="8" t="n">
-        <v>45908</v>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -1023,8 +1688,115 @@
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date réc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type rég</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N° doc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bq/Agce</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bq dép. - Agce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nom dép</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mont</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date éch</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Date créat</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>N° Facture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date fact</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/excel/cheques_2025.xlsx
+++ b/data/excel/cheques_2025.xlsx
@@ -1532,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1690,6 +1690,61 @@
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Al Barid Bank - dsdsd</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fikri El Fakir</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FIKRI EL FAKIR</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>23232</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>MAD</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>EN_ATTENTE</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
